--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_04-02-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_04-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="234">
   <si>
     <t>SKU</t>
   </si>
@@ -427,274 +427,238 @@
     <t>£498.04</t>
   </si>
   <si>
-    <t>£21.61</t>
-  </si>
-  <si>
-    <t>Cloudflare Blocked</t>
-  </si>
-  <si>
-    <t>£30.03</t>
-  </si>
-  <si>
-    <t>£31.68</t>
+    <t>£14.37</t>
+  </si>
+  <si>
+    <t>£16.73</t>
+  </si>
+  <si>
+    <t>£20.35</t>
+  </si>
+  <si>
+    <t>£23.36</t>
+  </si>
+  <si>
+    <t>£27.84</t>
+  </si>
+  <si>
+    <t>£30.43</t>
+  </si>
+  <si>
+    <t>£30.69</t>
+  </si>
+  <si>
+    <t>£33.61</t>
+  </si>
+  <si>
+    <t>£37.52</t>
+  </si>
+  <si>
+    <t>£39.20</t>
+  </si>
+  <si>
+    <t>£44.93</t>
+  </si>
+  <si>
+    <t>£46.33</t>
+  </si>
+  <si>
+    <t>£53.03</t>
+  </si>
+  <si>
+    <t>£56.74</t>
+  </si>
+  <si>
+    <t>£57.52</t>
+  </si>
+  <si>
+    <t>£54.58</t>
+  </si>
+  <si>
+    <t>£97.75</t>
+  </si>
+  <si>
+    <t>£91.31</t>
+  </si>
+  <si>
+    <t>£102.88</t>
+  </si>
+  <si>
+    <t>£116.93</t>
+  </si>
+  <si>
+    <t>£11.14</t>
+  </si>
+  <si>
+    <t>£13.29</t>
+  </si>
+  <si>
+    <t>£15.49</t>
+  </si>
+  <si>
+    <t>£17.49</t>
+  </si>
+  <si>
+    <t>£20.88</t>
+  </si>
+  <si>
+    <t>£23.46</t>
+  </si>
+  <si>
+    <t>£24.33</t>
+  </si>
+  <si>
+    <t>£26.97</t>
+  </si>
+  <si>
+    <t>£29.40</t>
+  </si>
+  <si>
+    <t>£36.27</t>
+  </si>
+  <si>
+    <t>£41.87</t>
+  </si>
+  <si>
+    <t>£42.62</t>
+  </si>
+  <si>
+    <t>£43.58</t>
+  </si>
+  <si>
+    <t>£89.15</t>
+  </si>
+  <si>
+    <t>£90.42</t>
+  </si>
+  <si>
+    <t>£428.72</t>
+  </si>
+  <si>
+    <t>£15.06</t>
+  </si>
+  <si>
+    <t>£18.35</t>
+  </si>
+  <si>
+    <t>£21.77</t>
+  </si>
+  <si>
+    <t>£22.90</t>
+  </si>
+  <si>
+    <t>£27.76</t>
+  </si>
+  <si>
+    <t>£28.75</t>
+  </si>
+  <si>
+    <t>£31.75</t>
+  </si>
+  <si>
+    <t>£35.05</t>
+  </si>
+  <si>
+    <t>£39.70</t>
+  </si>
+  <si>
+    <t>£88.80</t>
+  </si>
+  <si>
+    <t>£47.00</t>
+  </si>
+  <si>
+    <t>£53.54</t>
+  </si>
+  <si>
+    <t>£57.00</t>
+  </si>
+  <si>
+    <t>£58.00</t>
+  </si>
+  <si>
+    <t>£727.5</t>
+  </si>
+  <si>
+    <t>£10.48</t>
+  </si>
+  <si>
+    <t>£12.15</t>
+  </si>
+  <si>
+    <t>£15.26</t>
+  </si>
+  <si>
+    <t>£19.75</t>
+  </si>
+  <si>
+    <t>£25.47</t>
+  </si>
+  <si>
+    <t>£33.99</t>
+  </si>
+  <si>
+    <t>£33.38</t>
+  </si>
+  <si>
+    <t>£40.99</t>
+  </si>
+  <si>
+    <t>£42.35</t>
+  </si>
+  <si>
+    <t>£103.22</t>
+  </si>
+  <si>
+    <t>£89.41</t>
+  </si>
+  <si>
+    <t>£518.2</t>
+  </si>
+  <si>
+    <t>£513.3</t>
+  </si>
+  <si>
+    <t>£488.4</t>
+  </si>
+  <si>
+    <t>£10.06</t>
+  </si>
+  <si>
+    <t>£12.19</t>
+  </si>
+  <si>
+    <t>£14.71</t>
+  </si>
+  <si>
+    <t>£15.22</t>
+  </si>
+  <si>
+    <t>£19.88</t>
+  </si>
+  <si>
+    <t>£22.09</t>
+  </si>
+  <si>
+    <t>£21.69</t>
+  </si>
+  <si>
+    <t>£25.27</t>
+  </si>
+  <si>
+    <t>£26.55</t>
+  </si>
+  <si>
+    <t>£26.05</t>
+  </si>
+  <si>
+    <t>£32.42</t>
+  </si>
+  <si>
+    <t>£32.32</t>
   </si>
   <si>
     <t>£39.44</t>
-  </si>
-  <si>
-    <t>£45.56</t>
-  </si>
-  <si>
-    <t>£47.62</t>
-  </si>
-  <si>
-    <t>£52.32</t>
-  </si>
-  <si>
-    <t>£56.64</t>
-  </si>
-  <si>
-    <t>£46.38</t>
-  </si>
-  <si>
-    <t>£73.42</t>
-  </si>
-  <si>
-    <t>£72.38</t>
-  </si>
-  <si>
-    <t>£82.22</t>
-  </si>
-  <si>
-    <t>£89.12</t>
-  </si>
-  <si>
-    <t>£14.37</t>
-  </si>
-  <si>
-    <t>£16.73</t>
-  </si>
-  <si>
-    <t>£20.35</t>
-  </si>
-  <si>
-    <t>£23.36</t>
-  </si>
-  <si>
-    <t>£27.84</t>
-  </si>
-  <si>
-    <t>£30.43</t>
-  </si>
-  <si>
-    <t>£30.69</t>
-  </si>
-  <si>
-    <t>£33.61</t>
-  </si>
-  <si>
-    <t>£37.52</t>
-  </si>
-  <si>
-    <t>£39.20</t>
-  </si>
-  <si>
-    <t>£44.93</t>
-  </si>
-  <si>
-    <t>£46.33</t>
-  </si>
-  <si>
-    <t>£53.03</t>
-  </si>
-  <si>
-    <t>£56.74</t>
-  </si>
-  <si>
-    <t>£57.52</t>
-  </si>
-  <si>
-    <t>£54.58</t>
-  </si>
-  <si>
-    <t>£97.75</t>
-  </si>
-  <si>
-    <t>£91.31</t>
-  </si>
-  <si>
-    <t>£102.88</t>
-  </si>
-  <si>
-    <t>£116.93</t>
-  </si>
-  <si>
-    <t>£11.14</t>
-  </si>
-  <si>
-    <t>£13.29</t>
-  </si>
-  <si>
-    <t>£15.49</t>
-  </si>
-  <si>
-    <t>£17.49</t>
-  </si>
-  <si>
-    <t>£20.88</t>
-  </si>
-  <si>
-    <t>£23.46</t>
-  </si>
-  <si>
-    <t>£24.33</t>
-  </si>
-  <si>
-    <t>£26.97</t>
-  </si>
-  <si>
-    <t>£29.40</t>
-  </si>
-  <si>
-    <t>£36.27</t>
-  </si>
-  <si>
-    <t>£41.87</t>
-  </si>
-  <si>
-    <t>£42.62</t>
-  </si>
-  <si>
-    <t>£43.58</t>
-  </si>
-  <si>
-    <t>£89.15</t>
-  </si>
-  <si>
-    <t>£90.42</t>
-  </si>
-  <si>
-    <t>£428.72</t>
-  </si>
-  <si>
-    <t>£15.06</t>
-  </si>
-  <si>
-    <t>£18.35</t>
-  </si>
-  <si>
-    <t>£21.77</t>
-  </si>
-  <si>
-    <t>£22.90</t>
-  </si>
-  <si>
-    <t>£27.76</t>
-  </si>
-  <si>
-    <t>£28.75</t>
-  </si>
-  <si>
-    <t>£31.75</t>
-  </si>
-  <si>
-    <t>£35.05</t>
-  </si>
-  <si>
-    <t>£39.70</t>
-  </si>
-  <si>
-    <t>£88.80</t>
-  </si>
-  <si>
-    <t>£47.00</t>
-  </si>
-  <si>
-    <t>£53.54</t>
-  </si>
-  <si>
-    <t>£57.00</t>
-  </si>
-  <si>
-    <t>£58.00</t>
-  </si>
-  <si>
-    <t>£727.5</t>
-  </si>
-  <si>
-    <t>£10.48</t>
-  </si>
-  <si>
-    <t>£12.15</t>
-  </si>
-  <si>
-    <t>£15.26</t>
-  </si>
-  <si>
-    <t>£19.75</t>
-  </si>
-  <si>
-    <t>£25.47</t>
-  </si>
-  <si>
-    <t>£33.99</t>
-  </si>
-  <si>
-    <t>£33.38</t>
-  </si>
-  <si>
-    <t>£40.99</t>
-  </si>
-  <si>
-    <t>£42.35</t>
-  </si>
-  <si>
-    <t>£103.22</t>
-  </si>
-  <si>
-    <t>£89.41</t>
-  </si>
-  <si>
-    <t>£518.2</t>
-  </si>
-  <si>
-    <t>£513.3</t>
-  </si>
-  <si>
-    <t>£488.4</t>
-  </si>
-  <si>
-    <t>£12.19</t>
-  </si>
-  <si>
-    <t>£14.71</t>
-  </si>
-  <si>
-    <t>£15.22</t>
-  </si>
-  <si>
-    <t>£19.88</t>
-  </si>
-  <si>
-    <t>£22.09</t>
-  </si>
-  <si>
-    <t>£21.69</t>
-  </si>
-  <si>
-    <t>£25.27</t>
-  </si>
-  <si>
-    <t>£26.55</t>
-  </si>
-  <si>
-    <t>£26.05</t>
-  </si>
-  <si>
-    <t>£32.42</t>
-  </si>
-  <si>
-    <t>£32.32</t>
   </si>
   <si>
     <t>£40.05</t>
@@ -1194,34 +1158,34 @@
         <v>122</v>
       </c>
       <c r="I2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" t="s">
         <v>137</v>
       </c>
-      <c r="J2" t="s">
-        <v>151</v>
-      </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="L2" t="s">
         <v>90</v>
       </c>
       <c r="M2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="N2" t="s">
         <v>89</v>
       </c>
       <c r="O2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" t="s">
         <v>202</v>
       </c>
-      <c r="P2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>89</v>
-      </c>
       <c r="R2" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1250,34 +1214,34 @@
         <v>123</v>
       </c>
       <c r="I3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" t="s">
         <v>138</v>
       </c>
-      <c r="J3" t="s">
-        <v>152</v>
-      </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="L3" t="s">
         <v>90</v>
       </c>
       <c r="M3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="N3" t="s">
         <v>89</v>
       </c>
       <c r="O3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" t="s">
         <v>203</v>
       </c>
-      <c r="P3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>216</v>
-      </c>
       <c r="R3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1306,34 +1270,34 @@
         <v>124</v>
       </c>
       <c r="I4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" t="s">
         <v>139</v>
       </c>
-      <c r="J4" t="s">
-        <v>153</v>
-      </c>
       <c r="K4" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="L4" t="s">
         <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="N4" t="s">
         <v>89</v>
       </c>
       <c r="O4" t="s">
+        <v>190</v>
+      </c>
+      <c r="P4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4" t="s">
         <v>204</v>
       </c>
-      <c r="P4" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>217</v>
-      </c>
       <c r="R4" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1362,19 +1326,19 @@
         <v>125</v>
       </c>
       <c r="I5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J5" t="s">
         <v>140</v>
       </c>
-      <c r="J5" t="s">
-        <v>154</v>
-      </c>
       <c r="K5" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="L5" t="s">
         <v>90</v>
       </c>
       <c r="M5" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="N5" t="s">
         <v>89</v>
@@ -1386,10 +1350,10 @@
         <v>89</v>
       </c>
       <c r="Q5" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="R5" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1418,34 +1382,34 @@
         <v>126</v>
       </c>
       <c r="I6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" t="s">
         <v>141</v>
       </c>
-      <c r="J6" t="s">
-        <v>155</v>
-      </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="L6" t="s">
         <v>90</v>
       </c>
       <c r="M6" t="s">
+        <v>177</v>
+      </c>
+      <c r="N6" t="s">
+        <v>89</v>
+      </c>
+      <c r="O6" t="s">
         <v>191</v>
       </c>
-      <c r="N6" t="s">
-        <v>89</v>
-      </c>
-      <c r="O6" t="s">
-        <v>205</v>
-      </c>
       <c r="P6" t="s">
         <v>89</v>
       </c>
       <c r="Q6" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="R6" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1474,19 +1438,19 @@
         <v>127</v>
       </c>
       <c r="I7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" t="s">
         <v>142</v>
       </c>
-      <c r="J7" t="s">
-        <v>156</v>
-      </c>
       <c r="K7" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="L7" t="s">
         <v>90</v>
       </c>
       <c r="M7" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="N7" t="s">
         <v>89</v>
@@ -1498,10 +1462,10 @@
         <v>89</v>
       </c>
       <c r="Q7" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="R7" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1530,19 +1494,19 @@
         <v>128</v>
       </c>
       <c r="I8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" t="s">
         <v>143</v>
       </c>
-      <c r="J8" t="s">
-        <v>157</v>
-      </c>
       <c r="K8" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="L8" t="s">
         <v>90</v>
       </c>
       <c r="M8" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="N8" t="s">
         <v>89</v>
@@ -1554,10 +1518,10 @@
         <v>89</v>
       </c>
       <c r="Q8" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="R8" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1586,34 +1550,34 @@
         <v>129</v>
       </c>
       <c r="I9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" t="s">
         <v>144</v>
       </c>
-      <c r="J9" t="s">
-        <v>158</v>
-      </c>
       <c r="K9" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="L9" t="s">
         <v>90</v>
       </c>
       <c r="M9" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="N9" t="s">
         <v>89</v>
       </c>
       <c r="O9" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="P9" t="s">
         <v>89</v>
       </c>
       <c r="Q9" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="R9" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1642,13 +1606,13 @@
         <v>74</v>
       </c>
       <c r="I10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J10" t="s">
         <v>145</v>
       </c>
-      <c r="J10" t="s">
-        <v>159</v>
-      </c>
       <c r="K10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="L10" t="s">
         <v>90</v>
@@ -1666,10 +1630,10 @@
         <v>89</v>
       </c>
       <c r="Q10" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="R10" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1698,19 +1662,19 @@
         <v>75</v>
       </c>
       <c r="I11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" t="s">
         <v>146</v>
       </c>
-      <c r="J11" t="s">
-        <v>160</v>
-      </c>
       <c r="K11" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="L11" t="s">
         <v>90</v>
       </c>
       <c r="M11" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="N11" t="s">
         <v>89</v>
@@ -1722,10 +1686,10 @@
         <v>89</v>
       </c>
       <c r="Q11" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="R11" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1754,11 +1718,11 @@
         <v>90</v>
       </c>
       <c r="I12" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" t="s">
         <v>147</v>
       </c>
-      <c r="J12" t="s">
-        <v>161</v>
-      </c>
       <c r="K12" t="s">
         <v>90</v>
       </c>
@@ -1766,19 +1730,19 @@
         <v>90</v>
       </c>
       <c r="M12" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="N12" t="s">
         <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="P12" t="s">
         <v>89</v>
       </c>
       <c r="Q12" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="R12" t="s">
         <v>90</v>
@@ -1810,34 +1774,34 @@
         <v>130</v>
       </c>
       <c r="I13" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" t="s">
         <v>148</v>
       </c>
-      <c r="J13" t="s">
-        <v>162</v>
-      </c>
       <c r="K13" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s">
         <v>90</v>
       </c>
       <c r="M13" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="N13" t="s">
         <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="P13" t="s">
         <v>89</v>
       </c>
       <c r="Q13" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="R13" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1866,31 +1830,31 @@
         <v>131</v>
       </c>
       <c r="I14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" t="s">
         <v>149</v>
       </c>
-      <c r="J14" t="s">
-        <v>163</v>
-      </c>
       <c r="K14" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s">
         <v>90</v>
       </c>
       <c r="M14" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s">
         <v>89</v>
       </c>
       <c r="O14" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="P14" t="s">
         <v>89</v>
       </c>
       <c r="Q14" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="R14" t="s">
         <v>90</v>
@@ -1922,31 +1886,31 @@
         <v>132</v>
       </c>
       <c r="I15" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s">
         <v>90</v>
       </c>
       <c r="M15" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s">
         <v>89</v>
       </c>
       <c r="O15" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s">
         <v>89</v>
       </c>
       <c r="Q15" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="R15" t="s">
         <v>90</v>
@@ -1978,19 +1942,19 @@
         <v>133</v>
       </c>
       <c r="I16" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="K16" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s">
         <v>90</v>
       </c>
       <c r="M16" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s">
         <v>89</v>
@@ -2002,10 +1966,10 @@
         <v>89</v>
       </c>
       <c r="Q16" t="s">
+        <v>216</v>
+      </c>
+      <c r="R16" t="s">
         <v>228</v>
-      </c>
-      <c r="R16" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2093,7 +2057,7 @@
         <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
         <v>90</v>
@@ -2108,7 +2072,7 @@
         <v>89</v>
       </c>
       <c r="O18" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="P18" t="s">
         <v>89</v>
@@ -2117,7 +2081,7 @@
         <v>90</v>
       </c>
       <c r="R18" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2149,7 +2113,7 @@
         <v>90</v>
       </c>
       <c r="J19" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="K19" t="s">
         <v>90</v>
@@ -2164,7 +2128,7 @@
         <v>89</v>
       </c>
       <c r="O19" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s">
         <v>89</v>
@@ -2173,7 +2137,7 @@
         <v>90</v>
       </c>
       <c r="R19" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2205,7 +2169,7 @@
         <v>90</v>
       </c>
       <c r="J20" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="K20" t="s">
         <v>90</v>
@@ -2261,7 +2225,7 @@
         <v>90</v>
       </c>
       <c r="J21" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="K21" t="s">
         <v>90</v>
@@ -2317,7 +2281,7 @@
         <v>90</v>
       </c>
       <c r="J22" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="K22" t="s">
         <v>90</v>
@@ -2376,19 +2340,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="L23" t="s">
         <v>90</v>
       </c>
       <c r="M23" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="N23" t="s">
         <v>89</v>
       </c>
       <c r="O23" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="P23" t="s">
         <v>90</v>
@@ -2397,7 +2361,7 @@
         <v>90</v>
       </c>
       <c r="R23" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2432,7 +2396,7 @@
         <v>90</v>
       </c>
       <c r="K24" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s">
         <v>90</v>
@@ -2444,7 +2408,7 @@
         <v>89</v>
       </c>
       <c r="O24" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="P24" t="s">
         <v>90</v>
@@ -2453,7 +2417,7 @@
         <v>90</v>
       </c>
       <c r="R24" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2488,7 +2452,7 @@
         <v>90</v>
       </c>
       <c r="K25" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="L25" t="s">
         <v>90</v>
@@ -2500,7 +2464,7 @@
         <v>89</v>
       </c>
       <c r="O25" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="P25" t="s">
         <v>90</v>
@@ -2509,7 +2473,7 @@
         <v>90</v>
       </c>
       <c r="R25" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
